--- a/data/Vaentingar_markadsadila.xlsx
+++ b/data/Vaentingar_markadsadila.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29819"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29825"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\HAGFRAEDISVID\Innlendir fjármálamarkaðir\4. Markaðskönnun\2026\Q1 19. -21. janúar\B3. Excel skjal fyrir vef - birtingarskjal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CCC96EF3-C621-4682-A1F5-D964B0FD76B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{73F45585-CA77-4769-8896-455CC1C2375A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2730" yWindow="2730" windowWidth="38700" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data/Vaentingar_markadsadila.xlsx
+++ b/data/Vaentingar_markadsadila.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29825"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29917"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\HAGFRAEDISVID\Innlendir fjármálamarkaðir\4. Markaðskönnun\2026\Q1 19. -21. janúar\B3. Excel skjal fyrir vef - birtingarskjal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{73F45585-CA77-4769-8896-455CC1C2375A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9A27AEEE-6078-46E0-A3DB-830AB6734A6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2730" yWindow="2730" windowWidth="38700" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
